--- a/ExamOral_2026/RegistrationList_OralRe-exam_IDMA26_NDAB23002E.xlsx
+++ b/ExamOral_2026/RegistrationList_OralRe-exam_IDMA26_NDAB23002E.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\SUN-FAK-Studienaevn-Eksamen\SCIENCE Nørre\5. Tilmeldingslister\2025-2026\B2-3&amp;3 reeksamen\5100 DIKU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Teaching\IDMA26\ExamOral_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B12D4F57-C17F-467A-9283-151E1A9EE784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7EAECC-F32D-4835-BB90-0CBEE1305E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{166E2318-25DB-4B18-BA1E-F726B1372FA1}"/>
+    <workbookView xWindow="21857" yWindow="0" windowWidth="11143" windowHeight="19937" xr2:uid="{E8386445-9A6C-438D-A613-3C944DF45AF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="58">
   <si>
     <t>ADM</t>
   </si>
@@ -62,10 +62,19 @@
     <t>STUD_ID</t>
   </si>
   <si>
+    <t>STUD_NAVN</t>
+  </si>
+  <si>
     <t>TILM_STATUS</t>
   </si>
   <si>
-    <t>5100 Datalogisk Institut samt underordnede enheder</t>
+    <t>Kolonne1</t>
+  </si>
+  <si>
+    <t>MF (Skriv MF hvis MF, ellers blank)</t>
+  </si>
+  <si>
+    <t>Alle</t>
   </si>
   <si>
     <t>Termin         : Eksamen blok 3 2025-2026, reeksamen</t>
@@ -86,65 +95,134 @@
     <t>FKX388</t>
   </si>
   <si>
+    <t>Berg, Julius Willestofte</t>
+  </si>
+  <si>
     <t>tilmeldt</t>
   </si>
   <si>
+    <t>HMF512</t>
+  </si>
+  <si>
+    <t>Beyer-Nielsen, Oscar</t>
+  </si>
+  <si>
     <t>RWL997</t>
   </si>
   <si>
-    <t>ZRH830</t>
-  </si>
-  <si>
-    <t>ZQS981</t>
+    <t>Bøgh, Kian Kaarup</t>
   </si>
   <si>
     <t>CGQ654</t>
   </si>
   <si>
+    <t>Gleerup, Oliver Fisker</t>
+  </si>
+  <si>
     <t>FQM630</t>
   </si>
   <si>
+    <t>Jørgensen, Lauritz Tørholm</t>
+  </si>
+  <si>
     <t>CHV630</t>
   </si>
   <si>
+    <t>Kilic, Sevval Zana</t>
+  </si>
+  <si>
+    <t>LWH753</t>
+  </si>
+  <si>
+    <t>Kinsella, Kevin Jessen</t>
+  </si>
+  <si>
     <t>GHP118</t>
   </si>
   <si>
+    <t>Kristensen, Theodor</t>
+  </si>
+  <si>
     <t>HRT999</t>
   </si>
   <si>
+    <t>Lejre, Frej Berri</t>
+  </si>
+  <si>
+    <t>DQR746</t>
+  </si>
+  <si>
+    <t>Marshall, Lucas Ullerup</t>
+  </si>
+  <si>
+    <t>ZBT570</t>
+  </si>
+  <si>
+    <t>Marup, Emma-Maria</t>
+  </si>
+  <si>
+    <t>ZJM580</t>
+  </si>
+  <si>
+    <t>Mollerup, Gustav Ingels</t>
+  </si>
+  <si>
     <t>DPS824</t>
   </si>
   <si>
+    <t>Rasmussen, Lea Skov</t>
+  </si>
+  <si>
     <t>NPZ178</t>
   </si>
   <si>
-    <t>PRK315</t>
-  </si>
-  <si>
-    <t>Kolonne1</t>
-  </si>
-  <si>
-    <t>Kolonne2</t>
-  </si>
-  <si>
-    <t>MF (Skriv MF hvis MF, ellers blank)</t>
+    <t>Ridgewell, Abel Asrat</t>
+  </si>
+  <si>
+    <t>TZQ775</t>
+  </si>
+  <si>
+    <t>Skovborg, Noah Gyldenløve</t>
+  </si>
+  <si>
+    <t>LDS147</t>
+  </si>
+  <si>
+    <t>Strøyberg, Søren</t>
+  </si>
+  <si>
+    <t>GRL379</t>
+  </si>
+  <si>
+    <t>grl379, grl379</t>
+  </si>
+  <si>
+    <t>KCJ878</t>
+  </si>
+  <si>
+    <t>GPV679</t>
+  </si>
+  <si>
+    <t>Thorlund, Emil Roer</t>
+  </si>
+  <si>
+    <t>Nybo, Karl August Krogh</t>
+  </si>
+  <si>
+    <t>MF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   OK, but listed on both registration lists!?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -197,27 +275,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E0D30978-06AE-4D13-A3A2-767B6B84B201}" name="Tabel1" displayName="Tabel1" ref="A1:K13" totalsRowShown="0">
-  <autoFilter ref="A1:K13" xr:uid="{E0D30978-06AE-4D13-A3A2-767B6B84B201}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A600D665-1606-4CBB-88FF-E45B182D1D82}" name="Tabel1" displayName="Tabel1" ref="A1:K20" totalsRowShown="0">
+  <autoFilter ref="A1:K20" xr:uid="{A600D665-1606-4CBB-88FF-E45B182D1D82}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K18">
+    <sortCondition ref="G1:G18"/>
+  </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{79E6E6D3-BD16-4740-9C12-0723F43CCE87}" name="ADM"/>
-    <tableColumn id="2" xr3:uid="{F81244B1-4206-4DA0-BF09-CEEBBA7FE0AC}" name="TERMIN"/>
-    <tableColumn id="3" xr3:uid="{F175508B-B5ED-45A9-BABB-F9C193A1E0FF}" name="EKSAMENSTYPE"/>
-    <tableColumn id="4" xr3:uid="{835571E0-C8E8-45F5-B1E2-BB9BF0E74E62}" name="EKS_AKT_KODE"/>
-    <tableColumn id="5" xr3:uid="{108D67AF-4812-4C31-A746-481FA7743572}" name="VALG"/>
-    <tableColumn id="6" xr3:uid="{5BB4AA95-8C2F-497A-AB63-A41DD5A265B3}" name="EKS_AKT_NAVN"/>
-    <tableColumn id="7" xr3:uid="{D5884D5C-62F3-4FF2-84F5-09483C001308}" name="STUD_ID"/>
-    <tableColumn id="8" xr3:uid="{CF97E83F-EBCB-4F31-BCB3-87E95248C987}" name="TILM_STATUS"/>
-    <tableColumn id="9" xr3:uid="{7FA08898-D009-4CF8-8570-B3994EDE7683}" name="Kolonne1"/>
-    <tableColumn id="10" xr3:uid="{93DFBB72-7798-4EDB-8558-34264D3968B4}" name="Kolonne2"/>
-    <tableColumn id="11" xr3:uid="{FA6FEE58-C564-4C08-8E23-8F36CA6B3D2D}" name="MF (Skriv MF hvis MF, ellers blank)" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{2CD0BA00-5A03-4413-9295-997AE7D35652}" name="ADM"/>
+    <tableColumn id="2" xr3:uid="{8833588D-00E7-48D9-B796-61BA81C7CE7C}" name="TERMIN"/>
+    <tableColumn id="3" xr3:uid="{052F655C-D527-4365-B899-8BF021FAF847}" name="EKSAMENSTYPE"/>
+    <tableColumn id="4" xr3:uid="{71A5D4EB-BEA0-4251-84D9-C360A2F2FDC0}" name="EKS_AKT_KODE"/>
+    <tableColumn id="5" xr3:uid="{1273B07C-83C7-4C49-A6FE-42D792C7D476}" name="VALG"/>
+    <tableColumn id="6" xr3:uid="{D98CB33E-8FC5-46B8-9814-AB853771D61F}" name="EKS_AKT_NAVN"/>
+    <tableColumn id="7" xr3:uid="{DF2B44E0-5503-4EF7-BE09-8A8F81DC06B2}" name="STUD_ID"/>
+    <tableColumn id="8" xr3:uid="{5BEAB7D4-A877-4A40-826A-9842F0258F6C}" name="STUD_NAVN"/>
+    <tableColumn id="9" xr3:uid="{6456ECF4-6FE9-4F36-B521-E5E8E68C0067}" name="TILM_STATUS"/>
+    <tableColumn id="10" xr3:uid="{B8E2F9D8-D940-4C5D-8D90-B0DC00514D20}" name="Kolonne1"/>
+    <tableColumn id="11" xr3:uid="{72174EDC-643E-46C9-B6B9-7D905A21D76A}" name="MF (Skriv MF hvis MF, ellers blank)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-tema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -532,23 +613,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68819445-610E-460A-A4D5-4D75BA23AF98}">
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BA0B6FC-9CDD-4984-9E41-E2A1E1C9AE91}">
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="48" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.3046875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.69140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -574,345 +648,599 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" t="s">
         <v>27</v>
       </c>
-      <c r="J1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" t="s">
+        <v>51</v>
+      </c>
+      <c r="I9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" t="s">
         <v>20</v>
       </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="H10" t="s">
         <v>21</v>
       </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="I10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" t="s">
+        <v>45</v>
+      </c>
+      <c r="I14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" t="s">
         <v>22</v>
       </c>
-      <c r="H9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="H15" t="s">
         <v>23</v>
       </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-      <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" t="s">
-        <v>15</v>
-      </c>
-      <c r="K13" s="1"/>
+      <c r="I15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" t="s">
+        <v>47</v>
+      </c>
+      <c r="I16" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" t="s">
+        <v>38</v>
+      </c>
+      <c r="H17" t="s">
+        <v>39</v>
+      </c>
+      <c r="I17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" t="s">
+        <v>41</v>
+      </c>
+      <c r="I18" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" t="s">
+        <v>55</v>
+      </c>
+      <c r="I19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" t="s">
+        <v>54</v>
+      </c>
+      <c r="I20" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a3927f91-cda1-4696-af89-8c9f1ceffa91}" enabled="0" method="" siteId="{a3927f91-cda1-4696-af89-8c9f1ceffa91}" removed="1"/>
+</clbl:labelList>
 </file>